--- a/10. Communicatie/sjabloon_links.xlsx
+++ b/10. Communicatie/sjabloon_links.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\JiveDocumentation\10. Communicatie\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\JiveDocumentation\10. Communicatie\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4998232-6170-4387-B90A-7BEDE016D18D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B2D739A-B3EB-448F-B394-068951C7AE54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{72F6FAE1-3AFF-42D1-9832-ACCCD42F5209}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{72F6FAE1-3AFF-42D1-9832-ACCCD42F5209}"/>
   </bookViews>
   <sheets>
     <sheet name="verwijzen naar PinC" sheetId="4" r:id="rId1"/>
@@ -176,7 +176,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -214,6 +214,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Mono"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -248,7 +254,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
@@ -280,6 +286,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -299,9 +308,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Kantoorthema">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Thema">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -339,7 +348,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -445,7 +454,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -587,7 +596,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -761,7 +770,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A26CEBE2-0F8A-495C-89AB-A5AE077BA272}">
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:P5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="36.77734375" customWidth="1"/>
@@ -836,36 +845,23 @@
       <c r="O3" s="5"/>
       <c r="P3" s="5"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="1" t="str">
-        <f>CONCATENATE(B1,IFERROR(IF(FIND("?",B1)&gt;0,"&amp;","?"),"?"),"mtm_campaign=",B2,"&amp;mtm_kwd=",B3)</f>
+      <c r="B4" s="15" t="str">
+        <f>CONCATENATE(CONCATENATE(IFERROR(MID(B1,1,FIND("#",B1)-1),B1),IFERROR(IF(FIND("?",IFERROR(MID(B1,1,FIND("#",B1)-1),B1))&gt;0,"&amp;","?"),"?"),"mtm_campaign=",B2,"&amp;mtm_kwd=",B3),IFERROR(MID(B1,FIND("#",B1),99),""))</f>
         <v>https://provincies.incijfers.be/databank?jiveworkspace_guid=ff593898-a5fa-41de-bddc-ebf303c20587&amp;mtm_campaign=pinc-nieuwsbrief-mei-2021&amp;mtm_kwd=afval-algemeen</v>
       </c>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A6" s="9" t="s">
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A5" s="9" t="s">
         <v>29</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A6" r:id="rId1" location="matomo-urls-opstellen" display="Klik voor meer details en voorbeelden" xr:uid="{7864DFD9-BBB1-4350-B370-478549C47A02}"/>
+    <hyperlink ref="A5" r:id="rId1" location="matomo-urls-opstellen" display="Klik voor meer details en voorbeelden" xr:uid="{7864DFD9-BBB1-4350-B370-478549C47A02}"/>
     <hyperlink ref="B1" r:id="rId2" xr:uid="{1183021B-10FF-4AD0-BFBE-5F37ABE55BF6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -874,21 +870,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100936F8FED91617845B8AEE40909B55B39" ma:contentTypeVersion="9" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="fdd048e5dac583385d85172ba3b74e7c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="50990e7d-986b-48ed-b7c7-e36476cb9bc9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d1746dd66c24095ee243b6b7578615d7" ns2:_="">
     <xsd:import namespace="50990e7d-986b-48ed-b7c7-e36476cb9bc9"/>
@@ -1066,10 +1047,35 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D4FD8BEE-8873-449E-A338-98F2026C684D}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B20CB91D-FED1-447E-B613-85B1339A1856}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="50990e7d-986b-48ed-b7c7-e36476cb9bc9"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1091,19 +1097,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B20CB91D-FED1-447E-B613-85B1339A1856}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D4FD8BEE-8873-449E-A338-98F2026C684D}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="50990e7d-986b-48ed-b7c7-e36476cb9bc9"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>